--- a/data_processed/results_XGB_m3_gas_per_capitaincome.xlsx
+++ b/data_processed/results_XGB_m3_gas_per_capitaincome.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.8382" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.8381" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.51242256164551</v>
+        <v>17.54414749145508</v>
       </c>
       <c r="D2" t="n">
-        <v>5.32090425491333</v>
+        <v>5.331613063812256</v>
       </c>
     </row>
     <row r="3">
@@ -467,14 +467,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>59.62686157226562</v>
+        <v>35.0057487487793</v>
       </c>
       <c r="D3" t="n">
-        <v>18.11678504943848</v>
+        <v>10.63814067840576</v>
       </c>
     </row>
     <row r="4">
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>73.83086395263672</v>
+        <v>48.78534698486328</v>
       </c>
       <c r="D4" t="n">
-        <v>22.43247413635254</v>
+        <v>14.82571887969971</v>
       </c>
     </row>
     <row r="5">
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.930827140808105</v>
+        <v>59.44940948486328</v>
       </c>
       <c r="D5" t="n">
-        <v>3.017342567443848</v>
+        <v>18.06649398803711</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35.10504913330078</v>
+        <v>73.86474609375</v>
       </c>
       <c r="D6" t="n">
-        <v>10.66617679595947</v>
+        <v>22.4472713470459</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dwelling_size</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.47451019287109</v>
+        <v>9.787699699401855</v>
       </c>
       <c r="D7" t="n">
-        <v>14.72830104827881</v>
+        <v>2.974452257156372</v>
       </c>
     </row>
     <row r="8">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31.82709693908691</v>
+        <v>31.82991218566895</v>
       </c>
       <c r="D8" t="n">
-        <v>9.670217514038086</v>
+        <v>9.673013687133789</v>
       </c>
     </row>
     <row r="9">
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>52.81727981567383</v>
+        <v>52.79190063476562</v>
       </c>
       <c r="D9" t="n">
-        <v>16.04779052734375</v>
+        <v>16.04329872131348</v>
       </c>
     </row>
   </sheetData>
